--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2020_T2_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2020_T2_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>78</t>
+    <t>72</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.308</t>
-  </si>
-  <si>
-    <t>(0.053)</t>
-  </si>
-  <si>
-    <t>0.449</t>
-  </si>
-  <si>
-    <t>(0.057)</t>
-  </si>
-  <si>
-    <t>0.269</t>
-  </si>
-  <si>
-    <t>(0.051)</t>
-  </si>
-  <si>
-    <t>1.179</t>
-  </si>
-  <si>
-    <t>(0.385)</t>
-  </si>
-  <si>
-    <t>1.167</t>
-  </si>
-  <si>
-    <t>(0.192)</t>
-  </si>
-  <si>
-    <t>0.436</t>
-  </si>
-  <si>
-    <t>(0.101)</t>
+    <t>0.333</t>
+  </si>
+  <si>
+    <t>(0.056)</t>
+  </si>
+  <si>
+    <t>0.486</t>
+  </si>
+  <si>
+    <t>(0.059)</t>
+  </si>
+  <si>
+    <t>0.292</t>
+  </si>
+  <si>
+    <t>(0.054)</t>
+  </si>
+  <si>
+    <t>1.278</t>
+  </si>
+  <si>
+    <t>(0.415)</t>
+  </si>
+  <si>
+    <t>1.264</t>
+  </si>
+  <si>
+    <t>(0.204)</t>
+  </si>
+  <si>
+    <t>0.472</t>
+  </si>
+  <si>
+    <t>(0.108)</t>
   </si>
   <si>
     <t>38</t>
@@ -138,7 +138,7 @@
     <t>(0.300)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.219**</t>
-  </si>
-  <si>
-    <t>0.393***</t>
-  </si>
-  <si>
-    <t>0.441***</t>
-  </si>
-  <si>
-    <t>1.136</t>
-  </si>
-  <si>
-    <t>2.570***</t>
-  </si>
-  <si>
-    <t>1.248***</t>
+    <t>0.193*</t>
+  </si>
+  <si>
+    <t>0.356***</t>
+  </si>
+  <si>
+    <t>0.419***</t>
+  </si>
+  <si>
+    <t>1.038</t>
+  </si>
+  <si>
+    <t>2.473***</t>
+  </si>
+  <si>
+    <t>1.212***</t>
   </si>
 </sst>
 </file>
